--- a/WC2026_Predictions.xlsx
+++ b/WC2026_Predictions.xlsx
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.68</v>
+        <v>0.54</v>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="G6" s="6" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.66</v>
+        <v>0.76</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -1070,15 +1070,15 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2 - 1</t>
+          <t>3 - 0</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.54</v>
+        <v>0.4</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -1188,15 +1188,15 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2 - 1</t>
+          <t>2 - 0</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.55</v>
+        <v>0.31</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
@@ -1306,15 +1306,15 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.52</v>
+        <v>0.34</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>1 - 3</t>
+          <t>0 - 3</t>
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.61</v>
+        <v>0.82</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.55</v>
+        <v>0.72</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -1542,15 +1542,15 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2.52</v>
+        <v>2.73</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3 - 1</t>
+          <t>3 - 0</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.51</v>
+        <v>0.3</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -1601,15 +1601,15 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2 - 1</t>
+          <t>2 - 0</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -1660,15 +1660,15 @@
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.59</v>
+        <v>0.42</v>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>1 - 2</t>
+          <t>0 - 2</t>
         </is>
       </c>
       <c r="G19" s="6" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
@@ -1719,15 +1719,15 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2 - 1</t>
+          <t>2 - 0</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.07</v>
+        <v>0.97</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2.93</v>
+        <v>3.21</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
@@ -2132,15 +2132,15 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2 - 1</t>
+          <t>2 - 0</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.6</v>
+        <v>0.39</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -2191,15 +2191,15 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2 - 1</t>
+          <t>2 - 0</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.52</v>
+        <v>0.31</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G29" s="6" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="G30" s="6" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
@@ -2427,15 +2427,15 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2 - 1</t>
+          <t>2 - 0</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.7</v>
+        <v>0.39</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
@@ -2545,15 +2545,15 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2 - 1</t>
+          <t>2 - 0</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.53</v>
+        <v>0.32</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1.44</v>
+        <v>1.09</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.92</v>
+        <v>1.27</v>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.65</v>
+        <v>0.76</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
@@ -2703,59 +2703,59 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Jun 20</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="E37" s="4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>1 - 1</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="E37" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>2 - 1</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>Draw</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Sweden wins</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>Monterrey</t>
         </is>
       </c>
-      <c r="K37" s="4" t="n">
+      <c r="K37" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="L37" s="4" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
       </c>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
@@ -2899,15 +2899,15 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2 - 1</t>
+          <t>2 - 0</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.61</v>
+        <v>0.47</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1.08</v>
+        <v>0.91</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.72</v>
+        <v>0.55</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         </is>
       </c>
       <c r="E48" s="6" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="G48" s="6" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         </is>
       </c>
       <c r="G49" s="6" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
@@ -3666,15 +3666,15 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2 - 1</t>
+          <t>3 - 0</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.51</v>
+        <v>0.37</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
@@ -3784,15 +3784,15 @@
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>0.62</v>
+        <v>0.37</v>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>1 - 2</t>
+          <t>0 - 2</t>
         </is>
       </c>
       <c r="G55" s="6" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
@@ -3961,15 +3961,15 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>3 - 1</t>
+          <t>3 - 0</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.53</v>
+        <v>0.39</v>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="G59" s="4" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
@@ -4256,15 +4256,15 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>3 - 1</t>
+          <t>3 - 0</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="G65" s="4" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         </is>
       </c>
       <c r="E66" s="6" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="G66" s="6" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         </is>
       </c>
       <c r="E67" s="6" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="G67" s="6" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
@@ -4551,15 +4551,15 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2 - 1</t>
+          <t>2 - 0</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
@@ -4610,15 +4610,15 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2 - 1</t>
+          <t>3 - 0</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.53</v>
+        <v>0.25</v>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>2.62</v>
+        <v>2.93</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.47</v>
+        <v>0.25</v>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.52</v>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         </is>
       </c>
       <c r="G73" s="4" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
@@ -5206,10 +5206,10 @@
         <v>6</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" s="11" t="n">
         <v>7</v>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
@@ -5237,13 +5237,13 @@
         <v>0</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J11" s="11" t="n">
         <v>7</v>
@@ -5274,10 +5274,10 @@
         <v>4</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="13" t="n">
         <v>3</v>
@@ -5305,13 +5305,13 @@
         <v>3</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="J13" s="15" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>6</v>
       </c>
       <c r="H18" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="11" t="n">
         <v>4</v>
-      </c>
-      <c r="I18" s="11" t="n">
-        <v>2</v>
       </c>
       <c r="J18" s="11" t="n">
         <v>6</v>
@@ -5474,10 +5474,10 @@
         <v>2</v>
       </c>
       <c r="G19" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="13" t="n">
         <v>4</v>
-      </c>
-      <c r="H19" s="13" t="n">
-        <v>5</v>
       </c>
       <c r="I19" s="13" t="n">
         <v>-1</v>
@@ -5508,13 +5508,13 @@
         <v>3</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>8</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="J20" s="15" t="n">
         <v>0</v>
@@ -5612,10 +5612,10 @@
         <v>6</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J24" s="11" t="n">
         <v>9</v>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Turkiye</t>
         </is>
       </c>
       <c r="C26" s="13" t="n">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>Turkiye</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C27" s="15" t="n">
@@ -5711,13 +5711,13 @@
         <v>1</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>4</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J27" s="15" t="n">
         <v>2</v>
@@ -5815,10 +5815,10 @@
         <v>7</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J31" s="11" t="n">
         <v>9</v>
@@ -5846,13 +5846,13 @@
         <v>1</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H32" s="11" t="n">
         <v>4</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J32" s="11" t="n">
         <v>4</v>
@@ -5880,13 +5880,13 @@
         <v>1</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H33" s="13" t="n">
         <v>4</v>
       </c>
       <c r="I33" s="13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J33" s="13" t="n">
         <v>4</v>
@@ -6018,10 +6018,10 @@
         <v>6</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J38" s="11" t="n">
         <v>9</v>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
@@ -6067,17 +6067,17 @@
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C40" s="13" t="n">
         <v>3</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" s="13" t="n">
         <v>1</v>
@@ -6092,7 +6092,7 @@
         <v>-1</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -6111,22 +6111,22 @@
         <v>0</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G41" s="15" t="n">
-        <v>3</v>
-      </c>
       <c r="H41" s="15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="J41" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -6221,10 +6221,10 @@
         <v>6</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J45" s="11" t="n">
         <v>9</v>
@@ -6320,13 +6320,13 @@
         <v>3</v>
       </c>
       <c r="G48" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J48" s="15" t="n">
         <v>0</v>
@@ -6658,13 +6658,13 @@
         <v>1</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H60" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J60" s="11" t="n">
         <v>6</v>
@@ -6695,10 +6695,10 @@
         <v>4</v>
       </c>
       <c r="H61" s="13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I61" s="13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J61" s="13" t="n">
         <v>3</v>
@@ -6726,13 +6726,13 @@
         <v>3</v>
       </c>
       <c r="G62" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="J62" s="15" t="n">
         <v>0</v>
@@ -6830,10 +6830,10 @@
         <v>7</v>
       </c>
       <c r="H66" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J66" s="11" t="n">
         <v>9</v>
@@ -6929,13 +6929,13 @@
         <v>3</v>
       </c>
       <c r="G69" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H69" s="15" t="n">
         <v>7</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J69" s="15" t="n">
         <v>0</v>
@@ -7033,10 +7033,10 @@
         <v>8</v>
       </c>
       <c r="H73" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J73" s="11" t="n">
         <v>9</v>
@@ -7132,13 +7132,13 @@
         <v>2</v>
       </c>
       <c r="G76" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H76" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I76" s="15" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J76" s="15" t="n">
         <v>1</v>
@@ -7233,13 +7233,13 @@
         <v>0</v>
       </c>
       <c r="G80" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H80" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I80" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J80" s="11" t="n">
         <v>9</v>
@@ -7267,13 +7267,13 @@
         <v>1</v>
       </c>
       <c r="G81" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H81" s="11" t="n">
         <v>4</v>
       </c>
       <c r="I81" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" s="11" t="n">
         <v>6</v>
@@ -7301,13 +7301,13 @@
         <v>2</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H82" s="13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I82" s="13" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="J82" s="13" t="n">
         <v>1</v>
@@ -7433,12 +7433,12 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
           <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>Canada</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Turkiye</t>
         </is>
       </c>
     </row>
@@ -7526,12 +7526,12 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
           <t>Japan</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Sweden</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7689,6 +7689,7 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7724,10 +7725,15 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>SP Rating</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Big3 Players</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Big3 %</t>
         </is>
@@ -7755,9 +7761,12 @@
         <v>55</v>
       </c>
       <c r="G2" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H2" s="15" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="H2" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="15" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -7785,9 +7794,12 @@
         <v>68</v>
       </c>
       <c r="G3" s="15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H3" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -7815,9 +7827,12 @@
         <v>56</v>
       </c>
       <c r="G4" s="15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H4" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7845,9 +7860,12 @@
         <v>60</v>
       </c>
       <c r="G5" s="15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H5" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
@@ -7875,9 +7893,12 @@
         <v>62</v>
       </c>
       <c r="G6" s="15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H6" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -7905,9 +7926,12 @@
         <v>52</v>
       </c>
       <c r="G7" s="15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H7" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -7935,9 +7959,12 @@
         <v>65</v>
       </c>
       <c r="G8" s="15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H8" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -7965,9 +7992,12 @@
         <v>60</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" s="15" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -7995,9 +8025,12 @@
         <v>52</v>
       </c>
       <c r="G10" s="15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="15" t="inlineStr">
+      <c r="I10" s="15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8025,9 +8058,12 @@
         <v>66</v>
       </c>
       <c r="G11" s="15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H11" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="H11" s="15" t="inlineStr">
+      <c r="I11" s="15" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
@@ -8055,9 +8091,12 @@
         <v>58</v>
       </c>
       <c r="G12" s="15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H12" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="I12" s="15" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -8085,9 +8124,12 @@
         <v>44</v>
       </c>
       <c r="G13" s="15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H13" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="I13" s="15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8115,9 +8157,12 @@
         <v>58</v>
       </c>
       <c r="G14" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="15" t="inlineStr">
+      <c r="I14" s="15" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
@@ -8145,9 +8190,12 @@
         <v>48</v>
       </c>
       <c r="G15" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="H15" s="15" t="inlineStr">
+      <c r="I15" s="15" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
@@ -8175,9 +8223,12 @@
         <v>56</v>
       </c>
       <c r="G16" s="15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H16" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="I16" s="15" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
@@ -8205,9 +8256,12 @@
         <v>55</v>
       </c>
       <c r="G17" s="15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H17" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="15" t="inlineStr">
+      <c r="I17" s="15" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -8235,9 +8289,12 @@
         <v>70</v>
       </c>
       <c r="G18" s="15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H18" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="H18" s="15" t="inlineStr">
+      <c r="I18" s="15" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -8265,9 +8322,12 @@
         <v>72</v>
       </c>
       <c r="G19" s="15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H19" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="H19" s="15" t="inlineStr">
+      <c r="I19" s="15" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -8295,9 +8355,12 @@
         <v>65</v>
       </c>
       <c r="G20" s="15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H20" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="H20" s="15" t="inlineStr">
+      <c r="I20" s="15" t="inlineStr">
         <is>
           <t>69%</t>
         </is>
@@ -8325,9 +8388,12 @@
         <v>50</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H21" s="15" t="inlineStr">
+        <v>5.5</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -8355,9 +8421,12 @@
         <v>38</v>
       </c>
       <c r="G22" s="15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H22" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="H22" s="15" t="inlineStr">
+      <c r="I22" s="15" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -8385,9 +8454,12 @@
         <v>56</v>
       </c>
       <c r="G23" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="15" t="inlineStr">
+      <c r="I23" s="15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8415,9 +8487,12 @@
         <v>46</v>
       </c>
       <c r="G24" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="15" t="inlineStr">
+      <c r="I24" s="15" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -8445,9 +8520,12 @@
         <v>58</v>
       </c>
       <c r="G25" s="15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H25" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="H25" s="15" t="inlineStr">
+      <c r="I25" s="15" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -8475,9 +8553,12 @@
         <v>68</v>
       </c>
       <c r="G26" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="H26" s="15" t="inlineStr">
+      <c r="I26" s="15" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8505,9 +8586,12 @@
         <v>48</v>
       </c>
       <c r="G27" s="15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H27" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="15" t="inlineStr">
+      <c r="I27" s="15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8535,9 +8619,12 @@
         <v>58</v>
       </c>
       <c r="G28" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="15" t="inlineStr">
+      <c r="I28" s="15" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -8565,9 +8652,12 @@
         <v>64</v>
       </c>
       <c r="G29" s="15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H29" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="H29" s="15" t="inlineStr">
+      <c r="I29" s="15" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
@@ -8595,9 +8685,12 @@
         <v>67</v>
       </c>
       <c r="G30" s="15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H30" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="H30" s="15" t="inlineStr">
+      <c r="I30" s="15" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
@@ -8625,9 +8718,12 @@
         <v>46</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H31" s="15" t="inlineStr">
+        <v>5.5</v>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -8655,9 +8751,12 @@
         <v>58</v>
       </c>
       <c r="G32" s="15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H32" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="H32" s="15" t="inlineStr">
+      <c r="I32" s="15" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8685,9 +8784,12 @@
         <v>50</v>
       </c>
       <c r="G33" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="15" t="inlineStr">
+      <c r="I33" s="15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8715,9 +8817,12 @@
         <v>52</v>
       </c>
       <c r="G34" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="H34" s="15" t="inlineStr">
+      <c r="I34" s="15" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -8745,9 +8850,12 @@
         <v>68</v>
       </c>
       <c r="G35" s="15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H35" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="H35" s="15" t="inlineStr">
+      <c r="I35" s="15" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -8775,9 +8883,12 @@
         <v>40</v>
       </c>
       <c r="G36" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="15" t="inlineStr">
+      <c r="I36" s="15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8805,9 +8916,12 @@
         <v>50</v>
       </c>
       <c r="G37" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="15" t="inlineStr">
+      <c r="I37" s="15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8835,9 +8949,12 @@
         <v>54</v>
       </c>
       <c r="G38" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H38" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="H38" s="15" t="inlineStr">
+      <c r="I38" s="15" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -8865,9 +8982,12 @@
         <v>65</v>
       </c>
       <c r="G39" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H39" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="H39" s="15" t="inlineStr">
+      <c r="I39" s="15" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8895,9 +9015,12 @@
         <v>48</v>
       </c>
       <c r="G40" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H40" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="15" t="inlineStr">
+      <c r="I40" s="15" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -8925,9 +9048,12 @@
         <v>58</v>
       </c>
       <c r="G41" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H41" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="H41" s="15" t="inlineStr">
+      <c r="I41" s="15" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
@@ -8955,9 +9081,12 @@
         <v>72</v>
       </c>
       <c r="G42" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H42" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="H42" s="15" t="inlineStr">
+      <c r="I42" s="15" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -8985,9 +9114,12 @@
         <v>60</v>
       </c>
       <c r="G43" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="H43" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="H43" s="15" t="inlineStr">
+      <c r="I43" s="15" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -9015,9 +9147,12 @@
         <v>64</v>
       </c>
       <c r="G44" s="15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H44" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="H44" s="15" t="inlineStr">
+      <c r="I44" s="15" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
@@ -9045,9 +9180,12 @@
         <v>54</v>
       </c>
       <c r="G45" s="15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H45" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="H45" s="15" t="inlineStr">
+      <c r="I45" s="15" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -9075,9 +9213,12 @@
         <v>58</v>
       </c>
       <c r="G46" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H46" s="15" t="inlineStr">
+        <v>6.5</v>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" s="15" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -9105,9 +9246,12 @@
         <v>62</v>
       </c>
       <c r="G47" s="15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H47" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="H47" s="15" t="inlineStr">
+      <c r="I47" s="15" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
@@ -9135,9 +9279,12 @@
         <v>63</v>
       </c>
       <c r="G48" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H48" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="H48" s="15" t="inlineStr">
+      <c r="I48" s="15" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
@@ -9165,9 +9312,12 @@
         <v>50</v>
       </c>
       <c r="G49" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H49" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="15" t="inlineStr">
+      <c r="I49" s="15" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
